--- a/Control Algorithms/V0/v0_signal_names.xlsx
+++ b/Control Algorithms/V0/v0_signal_names.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\coeit.osu.edu\home\k\kara.28\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GITHUB\FB26_Controls\Control Algorithms\V0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AB6A724-B1A2-4599-A11A-C7B5EAB21F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7030BD-6095-42D7-BC63-BFD8571C44F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{6408ACC7-8B01-4673-96AC-DFD7837C0511}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6408ACC7-8B01-4673-96AC-DFD7837C0511}"/>
   </bookViews>
   <sheets>
     <sheet name="Signal Names" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="150">
   <si>
     <t>Signal</t>
   </si>
@@ -444,9 +444,6 @@
     <t>BRK_F</t>
   </si>
   <si>
-    <t>Bar</t>
-  </si>
-  <si>
     <t>Ay</t>
   </si>
   <si>
@@ -457,6 +454,39 @@
   </si>
   <si>
     <t>deg</t>
+  </si>
+  <si>
+    <t>deg/s</t>
+  </si>
+  <si>
+    <t>Signal from 0 -&gt; 1</t>
+  </si>
+  <si>
+    <t>rpm</t>
+  </si>
+  <si>
+    <t>MPa</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>Tire Cornering Stiffness</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>N/deg</t>
+  </si>
+  <si>
+    <t>The ~slope from (0,0) to the peak of the alpha Fy plot at nominal loading</t>
+  </si>
+  <si>
+    <t>Vehicle Mass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kg </t>
   </si>
 </sst>
 </file>
@@ -879,7 +909,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -901,7 +931,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -914,6 +944,9 @@
       <c r="C6" t="s">
         <v>4</v>
       </c>
+      <c r="D6" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -923,7 +956,7 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -934,7 +967,7 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1160,21 +1193,21 @@
         <v>134</v>
       </c>
       <c r="C28" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1184,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29BE85F6-1FC1-42B5-84CF-C5ABF5A75E2B}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.140625" bestFit="1" customWidth="1"/>
@@ -1604,6 +1637,37 @@
         <v>128</v>
       </c>
     </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26">
+        <v>400</v>
+      </c>
+      <c r="D26" t="s">
+        <v>146</v>
+      </c>
+      <c r="E26" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>148</v>
+      </c>
+      <c r="B27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27">
+        <v>278</v>
+      </c>
+      <c r="D27" t="s">
+        <v>149</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Control Algorithms/V0/v0_signal_names.xlsx
+++ b/Control Algorithms/V0/v0_signal_names.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GITHUB\FB26_Controls\Control Algorithms\V0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7030BD-6095-42D7-BC63-BFD8571C44F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A2D5AE-EC1F-47EA-810D-A2E058578E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6408ACC7-8B01-4673-96AC-DFD7837C0511}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6408ACC7-8B01-4673-96AC-DFD7837C0511}"/>
   </bookViews>
   <sheets>
     <sheet name="Signal Names" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="156">
   <si>
     <t>Signal</t>
   </si>
@@ -487,6 +487,24 @@
   </si>
   <si>
     <t xml:space="preserve">kg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPM to Radians Per Second Converstion </t>
+  </si>
+  <si>
+    <t>rpm_to_radpers</t>
+  </si>
+  <si>
+    <t>rad/rpm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Degrees to Radians Converstion </t>
+  </si>
+  <si>
+    <t>degrees_to_radians</t>
+  </si>
+  <si>
+    <t>rad/deg</t>
   </si>
 </sst>
 </file>
@@ -1217,7 +1235,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29BE85F6-1FC1-42B5-84CF-C5ABF5A75E2B}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.140625" bestFit="1" customWidth="1"/>
@@ -1668,6 +1686,34 @@
         <v>149</v>
       </c>
     </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>150</v>
+      </c>
+      <c r="B28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C28">
+        <v>0.10471999999999999</v>
+      </c>
+      <c r="D28" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>153</v>
+      </c>
+      <c r="B29" t="s">
+        <v>154</v>
+      </c>
+      <c r="C29">
+        <v>1.7477220000000002E-2</v>
+      </c>
+      <c r="D29" t="s">
+        <v>155</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Control Algorithms/V0/v0_signal_names.xlsx
+++ b/Control Algorithms/V0/v0_signal_names.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GITHUB\FB26_Controls\Control Algorithms\V0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A2D5AE-EC1F-47EA-810D-A2E058578E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530DB3A8-1895-4C12-B300-BD23A05D34D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6408ACC7-8B01-4673-96AC-DFD7837C0511}"/>
+    <workbookView xWindow="57480" yWindow="-315" windowWidth="15600" windowHeight="11040" xr2:uid="{6408ACC7-8B01-4673-96AC-DFD7837C0511}"/>
   </bookViews>
   <sheets>
     <sheet name="Signal Names" sheetId="1" r:id="rId1"/>
